--- a/00_PROJECT_CONTROL/FINANCIAL_REGISTER.xlsx
+++ b/00_PROJECT_CONTROL/FINANCIAL_REGISTER.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANCIAL_REGISTER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Finance ID</t>
+          <t>Financial ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Revision</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -444,7 +444,8423 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Repository Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FIN-000001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AST-000001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DPR_Rev_1_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/DPR_Rev_1_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FIN-000002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AST-000002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DPR_Rev_2_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/DPR_Rev_2_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FIN-000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AST-000003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DPR_Rev_3_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/DPR_Rev_3_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FIN-000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AST-000004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DPR_Rev_4_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/DPR_Rev_4_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FIN-000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AST-000005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DPR_Rev_5_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/DPR_Rev_5_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FIN-000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AST-000006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev1.xlsx</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FIN-000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AST-000007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev10.xlsx</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev10.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FIN-000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AST-000008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev11.xlsx</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev11.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FIN-000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AST-000009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev12.xlsx</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev12.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FIN-000010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AST-000010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev13.xlsx</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev13.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FIN-000011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AST-000011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev1_Master (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev1_Master (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FIN-000012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AST-000012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev1_Master.xlsx</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev1_Master.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FIN-000013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AST-000013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev2 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev2 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FIN-000014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AST-000014</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev2.xlsx</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FIN-000015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AST-000015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev3.xlsx</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FIN-000016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AST-000016</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev4.xlsx</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FIN-000017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AST-000017</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev5.xlsx</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev5.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FIN-000018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AST-000018</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev6.xlsx</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev6.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FIN-000019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AST-000019</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev7.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev7.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FIN-000020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AST-000020</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev8.xlsx</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev8.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FIN-000021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AST-000021</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev9.xlsx</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_Engineering_Rev9.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FIN-000022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AST-000022</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_BuildQueue.xlsx</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_BuildQueue.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FIN-000023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AST-000023</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC.xlsx</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FIN-000024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AST-000024</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint1.xlsx</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FIN-000025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AST-000025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint10.xlsx</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint10.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FIN-000026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AST-000026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint11.xlsx</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint11.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FIN-000027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AST-000027</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint12.xlsx</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint12.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FIN-000028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AST-000028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint13.xlsx</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint13.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FIN-000029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AST-000029</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint13_RevA.xlsx</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint13_RevA.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FIN-000030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AST-000030</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint14.xlsx</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint14.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FIN-000031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AST-000031</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint15.xlsx</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint15.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FIN-000032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AST-000032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint16.xlsx</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint16.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FIN-000033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AST-000033</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint17.xlsx</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint17.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FIN-000034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AST-000034</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint18.xlsx</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint18.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FIN-000035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AST-000035</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint19.xlsx</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint19.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FIN-000036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AST-000036</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint2.xlsx</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FIN-000037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AST-000037</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint20.xlsx</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint20.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FIN-000038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AST-000038</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint3.xlsx</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FIN-000039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AST-000039</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint4.xlsx</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FIN-000040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AST-000040</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint5.xlsx</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint5.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FIN-000041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AST-000041</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint6.xlsx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint6.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FIN-000042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AST-000042</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint7.xlsx</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint7.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FIN-000043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AST-000043</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint8.xlsx</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint8.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FIN-000044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AST-000044</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint9.xlsx</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_RC_Sprint9.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FIN-000045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AST-000045</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING.xlsx</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FIN-000046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AST-000046</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle1.xlsx</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FIN-000047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AST-000047</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle1_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle1_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FIN-000048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AST-000048</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle1_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle1_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FIN-000049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AST-000049</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle1_Update.xlsx</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle1_Update.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FIN-000050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AST-000050</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle2.xlsx</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>FIN-000051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AST-000051</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle2_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_ImplCycle2_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FIN-000052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AST-000052</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1.xlsx</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FIN-000053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AST-000053</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1B.xlsx</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1B.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FIN-000054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AST-000054</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1C.xlsx</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1C.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FIN-000055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AST-000055</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1D.xlsx</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1D.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FIN-000056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AST-000056</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1E.xlsx</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1E.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FIN-000057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AST-000057</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1F.xlsx</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1F.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>FIN-000058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AST-000058</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1G.xlsx</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1G.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FIN-000059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AST-000059</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1H.xlsx</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_Phase1H.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FIN-000060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AST-000060</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueBusinessLogicReview.xlsx</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueBusinessLogicReview.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FIN-000061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AST-000061</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueClassification.xlsx</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueClassification.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FIN-000062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AST-000062</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueModel_Inspection.xlsx</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueModel_Inspection.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FIN-000063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AST-000063</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueModuleAudit.xlsx</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueModuleAudit.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FIN-000064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AST-000064</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueRefactorDecisions.xlsx</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueRefactorDecisions.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FIN-000065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AST-000065</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueRefactorReview.xlsx</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.0_WORKING_RevenueRefactorReview.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FIN-000066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AST-000066</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.1_REFACTORED_GOVERNANCE.xlsx</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.1_REFACTORED_GOVERNANCE.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FIN-000067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AST-000067</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.2_RF02.xlsx</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.2_RF02.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FIN-000068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AST-000068</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.3_RF02_Revenue_Integration.xlsx</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.3_RF02_Revenue_Integration.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FIN-000069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AST-000069</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.4_RF03_InPlace_Refactor.xlsx</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.4_RF03_InPlace_Refactor.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FIN-000070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AST-000070</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.5_Build100_Control.xlsx</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.5_Build100_Control.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FIN-000071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AST-000071</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.6.1_Build100_1_NoWarnings (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.6.1_Build100_1_NoWarnings (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FIN-000072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AST-000072</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.6.1_Build100_1_NoWarnings.xlsx</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.6.1_Build100_1_NoWarnings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FIN-000073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AST-000073</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.7_Refactor_Roadmap.xlsx</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.7_Refactor_Roadmap.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FIN-000074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AST-000074</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.8_Build101_Engineering.xlsx</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.8_Build101_Engineering.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FIN-000075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AST-000075</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.9_Engineering_Workspace.xlsx</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v1.9_Engineering_Workspace.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FIN-000076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AST-000076</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v2.0_Build102.xlsx</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v2.0_Build102.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FIN-000077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AST-000077</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v2.1_Build103.xlsx</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v2.1_Build103.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FIN-000078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AST-000078</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v2.2_Build104.xlsx</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v2.2_Build104.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FIN-000079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AST-000079</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v2.3_Build105.xlsx</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_Bankable_DPR_Financial_Model_v2.3_Build105.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FIN-000080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AST-000080</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_DPR_Production_Build_1_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_DPR_Production_Build_1_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FIN-000081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AST-000081</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_DPR_Production_Build_2_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_DPR_Production_Build_2_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FIN-000082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AST-000082</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_DPR_Production_Build_4_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_DPR_Production_Build_4_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FIN-000083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AST-000083</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_DPR_Production_Build_5_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_DPR_Production_Build_5_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FIN-000084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>AST-000084</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_DPR_Production_Build_6_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DPR</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_DPR_Production_Build_6_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FIN-000085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AST-000085</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>XOLANI_Eco_Resort_Financial_Model_v1.xlsx</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Eco_Resort_Financial_Model_v1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FIN-000086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AST-000086</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>XOLANI_Eco_Resort_Financial_Model_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Eco_Resort_Financial_Model_v2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>FIN-000087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AST-000087</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_RC1_Revenue_Engine.xlsx</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_RC1_Revenue_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FIN-000088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>AST-000088</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_RC1_Revenue_Engine_v2.xlsx</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_RC1_Revenue_Engine_v2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>FIN-000089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AST-000089</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_RC2_Operating_Cost_Engine.xlsx</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_RC2_Operating_Cost_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FIN-000090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>AST-000090</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>XOLANI_ECO_RESORT_RC3_Integrated_Financial_Model.xlsx</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_ECO_RESORT_RC3_Integrated_Financial_Model.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FIN-000091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AST-000091</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev10_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev10_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FIN-000092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AST-000092</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev10_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev10_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FIN-000093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AST-000093</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev10_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev10_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FIN-000094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AST-000094</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev11_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev11_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FIN-000095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AST-000095</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev11_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev11_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FIN-000096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AST-000096</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev12_0 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev12_0 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FIN-000097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AST-000097</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev12_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev12_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FIN-000098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AST-000098</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev12_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev12_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FIN-000099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AST-000099</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev13_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev13_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FIN-000100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>AST-000100</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev13_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev13_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FIN-000101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AST-000101</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev14_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev14_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FIN-000102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AST-000102</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev14_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev14_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FIN-000103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AST-000103</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev15_0 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev15_0 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FIN-000104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>AST-000104</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev15_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev15_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FIN-000105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>AST-000105</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev15_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev15_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FIN-000106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>AST-000106</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev16_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev16_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FIN-000107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>AST-000107</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev16_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev16_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FIN-000108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>AST-000108</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>FIN-000109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>AST-000109</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_1_Rebuilt.xlsx</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_1_Rebuilt.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FIN-000110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>AST-000110</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FIN-000111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>AST-000111</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>FIN-000112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>AST-000112</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_4.xlsx</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FIN-000113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>AST-000113</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_5.xlsx</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_5.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>FIN-000114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>AST-000114</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_6.xlsx</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_6.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>FIN-000115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>AST-000115</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_7.xlsx</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_7.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FIN-000116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>AST-000116</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_8.xlsx</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_8.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FIN-000117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>AST-000117</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev1_9.xlsx</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev1_9.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FIN-000118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>AST-000118</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev2_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev2_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FIN-000119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AST-000119</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev2_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev2_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FIN-000120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>AST-000120</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev2_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev2_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FIN-000121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>AST-000121</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev2_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev2_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>FIN-000122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>AST-000122</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev2_4 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev2_4 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FIN-000123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>AST-000123</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev2_4.xlsx</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev2_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>FIN-000124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>AST-000124</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev3_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev3_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FIN-000125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>AST-000125</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev3_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev3_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FIN-000126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>AST-000126</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev3_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev3_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>FIN-000127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>AST-000127</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev4_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev4_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>FIN-000128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>AST-000128</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev4_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev4_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FIN-000129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>AST-000129</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev4_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev4_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FIN-000130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>AST-000130</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev5_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev5_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FIN-000131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>AST-000131</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev5_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev5_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FIN-000132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>AST-000132</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev5_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev5_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FIN-000133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AST-000133</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev6_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev6_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FIN-000134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>AST-000134</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev6_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev6_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>FIN-000135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>AST-000135</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev6_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev6_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FIN-000136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>AST-000136</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev7_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev7_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FIN-000137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AST-000137</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev7_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev7_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FIN-000138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>AST-000138</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev8_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev8_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>FIN-000139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>AST-000139</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev8_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev8_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FIN-000140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>AST-000140</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev9_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev9_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FIN-000141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>AST-000141</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev9_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev9_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FIN-000142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>AST-000142</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev9_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev9_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FIN-000143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>AST-000143</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev9_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev9_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FIN-000144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>AST-000144</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Engine_Rev9_4.xlsx</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Engine_Rev9_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>FIN-000145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>AST-000145</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev10_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev10_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FIN-000146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>AST-000146</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev10_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev10_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FIN-000147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>AST-000147</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev11_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev11_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>FIN-000148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>AST-000148</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev11_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev11_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>FIN-000149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>AST-000149</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev12_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev12_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>FIN-000150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>AST-000150</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev12_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev12_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>FIN-000151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>AST-000151</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev13_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev13_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>FIN-000152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>AST-000152</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev13_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev13_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>FIN-000153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>AST-000153</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev14_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev14_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>FIN-000154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>AST-000154</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev14_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev14_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>FIN-000155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>AST-000155</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev15_0 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev15_0 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>FIN-000156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>AST-000156</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev15_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev15_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FIN-000157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>AST-000157</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev15_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev15_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>FIN-000158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>AST-000158</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev16_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev16_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>FIN-000159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>AST-000159</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev16_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev16_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>FIN-000160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>AST-000160</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev17_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev17_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>FIN-000161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>AST-000161</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev17_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev17_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>FIN-000162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>AST-000162</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev17_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev17_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>FIN-000163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>AST-000163</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev18_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev18_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FIN-000164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>AST-000164</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev18_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev18_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>FIN-000165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>AST-000165</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev19_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev19_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>FIN-000166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>AST-000166</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev19_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev19_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>FIN-000167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>AST-000167</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev20_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev20_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>FIN-000168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>AST-000168</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev20_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev20_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>FIN-000169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>AST-000169</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev21_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev21_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>FIN-000170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>AST-000170</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev21_1 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev21_1 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>FIN-000171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>AST-000171</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev21_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev21_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>FIN-000172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>AST-000172</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev22_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev22_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>FIN-000173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>AST-000173</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev22_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev22_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>FIN-000174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>AST-000174</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev23_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev23_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>FIN-000175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>AST-000175</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev23_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev23_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>FIN-000176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>AST-000176</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev24_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev24_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>FIN-000177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>AST-000177</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev24_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev24_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>FIN-000178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>AST-000178</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev25_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev25_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FIN-000179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>AST-000179</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev25_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev25_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FIN-000180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>AST-000180</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev26_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev26_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>FIN-000181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>AST-000181</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev26_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev26_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>FIN-000182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>AST-000182</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev27_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev27_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>FIN-000183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>AST-000183</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev27_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev27_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>FIN-000184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>AST-000184</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev28_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev28_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>FIN-000185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>AST-000185</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev28_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev28_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>FIN-000186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>AST-000186</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev29_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev29_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>FIN-000187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>AST-000187</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev29_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev29_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>FIN-000188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>AST-000188</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev30_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev30_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>FIN-000189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>AST-000189</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev30_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev30_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>FIN-000190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>AST-000190</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev31_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev31_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>FIN-000191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>AST-000191</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev31_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev31_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>FIN-000192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>AST-000192</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev32_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev32_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>FIN-000193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>AST-000193</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev32_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev32_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>FIN-000194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>AST-000194</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev33_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev33_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>FIN-000195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>AST-000195</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev33_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev33_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FIN-000196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>AST-000196</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev34_0 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev34_0 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FIN-000197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>AST-000197</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev34_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev34_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>FIN-000198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>AST-000198</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev34_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev34_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>FIN-000199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>AST-000199</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev35_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev35_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>FIN-000200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>AST-000200</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev35_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev35_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>FIN-000201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>AST-000201</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev36_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev36_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>FIN-000202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>AST-000202</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev36_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev36_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>FIN-000203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>AST-000203</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev37_0 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev37_0 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>FIN-000204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>AST-000204</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev37_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev37_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>FIN-000205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>AST-000205</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev37_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev37_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>FIN-000206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>AST-000206</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev38_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev38_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>FIN-000207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>AST-000207</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev38_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev38_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>FIN-000208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>AST-000208</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev39_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev39_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>FIN-000209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>AST-000209</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev39_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev39_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>FIN-000210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>AST-000210</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev3_0A.xlsx</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev3_0A.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>FIN-000211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AST-000211</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev3_0B.xlsx</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev3_0B.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>FIN-000212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>AST-000212</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev3_0C.xlsx</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev3_0C.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>FIN-000213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>AST-000213</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev3_0D.xlsx</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev3_0D.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>FIN-000214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>AST-000214</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev3_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev3_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>FIN-000215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>AST-000215</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev3_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev3_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>FIN-000216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>AST-000216</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev3_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev3_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>FIN-000217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>AST-000217</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev3_4.xlsx</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev3_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>FIN-000218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>AST-000218</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev40_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev40_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>FIN-000219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>AST-000219</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev40_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev40_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>FIN-000220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>AST-000220</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev40_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev40_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>FIN-000221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>AST-000221</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev40_4.xlsx</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev40_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>FIN-000222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>AST-000222</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev40_5.xlsx</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev40_5.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>FIN-000223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>AST-000223</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev40_6.xlsx</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev40_6.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>FIN-000224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>AST-000224</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev40_7.xlsx</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev40_7.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>FIN-000225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>AST-000225</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev4_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev4_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>FIN-000226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>AST-000226</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev4_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev4_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>FIN-000227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>AST-000227</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev4_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev4_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>FIN-000228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>AST-000228</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev4_3 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev4_3 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>FIN-000229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>AST-000229</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev4_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev4_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>FIN-000230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>AST-000230</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev4_4.xlsx</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev4_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>FIN-000231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>AST-000231</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev5_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev5_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>FIN-000232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>AST-000232</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev5_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev5_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>FIN-000233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>AST-000233</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev5_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev5_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>FIN-000234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>AST-000234</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev5_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev5_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>FIN-000235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>AST-000235</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev5_4.xlsx</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev5_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>FIN-000236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>AST-000236</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev5_5.xlsx</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev5_5.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FIN-000237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>AST-000237</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev5_6 (1).xlsx</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev5_6 (1).xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>FIN-000238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>AST-000238</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev5_6.xlsx</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev5_6.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>FIN-000239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>AST-000239</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev6_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev6_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FIN-000240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>AST-000240</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev6_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev6_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>FIN-000241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>AST-000241</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev6_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev6_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>FIN-000242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>AST-000242</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev7_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev7_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>FIN-000243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>AST-000243</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev7_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev7_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>FIN-000244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>AST-000244</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev7_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev7_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>FIN-000245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>AST-000245</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev7_3.xlsx</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev7_3.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>FIN-000246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>AST-000246</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev8_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev8_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>FIN-000247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>AST-000247</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev8_1.xlsx</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev8_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>FIN-000248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>AST-000248</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev8_2.xlsx</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev8_2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>FIN-000249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>AST-000249</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Master_Rev9_0.xlsx</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Master_Rev9_0.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>FIN-000250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>AST-000250</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>XOLANI_Financial_Model_Rev2.2.xlsx</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_Financial_Model_Rev2.2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>FIN-000251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>AST-000251</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint1_Workbook_Skeleton.xlsx</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint1_Workbook_Skeleton.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>FIN-000252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>AST-000252</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint2.1_Master_Assumptions_Governed.xlsx</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint2.1_Master_Assumptions_Governed.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>FIN-000253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>AST-000253</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint2.2_Master_Data_Warehouse.xlsx</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint2.2_Master_Data_Warehouse.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>FIN-000254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>AST-000254</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint2_Master_Assumptions.xlsx</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint2_Master_Assumptions.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>FIN-000255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>AST-000255</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint3.1_Production_Revenue_Engine.xlsx</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint3.1_Production_Revenue_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>FIN-000256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>AST-000256</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint3_Revenue_Engine_Skeleton.xlsx</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint3_Revenue_Engine_Skeleton.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>FIN-000257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>AST-000257</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint4.1_Dynamic_Payroll.xlsx</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint4.1_Dynamic_Payroll.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>FIN-000258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>AST-000258</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint4_Payroll_Engine.xlsx</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint4_Payroll_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>FIN-000259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>AST-000259</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint5_OPEX_Engine.xlsx</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint5_OPEX_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>FIN-000260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>AST-000260</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint6_CAPEX_Engine.xlsx</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint6_CAPEX_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>FIN-000261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>AST-000261</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint7_Financing_Engine.xlsx</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint7_Financing_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>FIN-000262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>AST-000262</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint8_Financial_Statements_Engine.xlsx</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint8_Financial_Statements_Engine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>FIN-000263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>AST-000263</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>XOLANI_IPFP_v1.0_Sprint9_Integration_Audit_Dashboard.xlsx</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>finance/XOLANI_Finance/XOLANI_IPFP_v1.0_Sprint9_Integration_Audit_Dashboard.xlsx</t>
         </is>
       </c>
     </row>
